--- a/Code/keywords.xlsx
+++ b/Code/keywords.xlsx
@@ -19,7 +19,7 @@
     <t>Demokrati/rettigheter</t>
   </si>
   <si>
-    <t>Kontroll/sikkerhet</t>
+    <t>Overvåkning/kontroll</t>
   </si>
   <si>
     <t>Økonomi/konkurranseevne</t>
